--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2021_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2021_tarapaca.xlsx
@@ -63,7 +63,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-18 11:10</t>
+    <t xml:space="preserve">2026-09-06 19:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
